--- a/TestCases/Booking_TestCase.xlsx
+++ b/TestCases/Booking_TestCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E781DED-A1BE-47F8-A119-0BEE4D9E46B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65AC02F-5AC2-4526-A2DE-D206E40DBE6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10056" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12012" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOOKING" sheetId="5" r:id="rId1"/>
@@ -23,12 +23,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
   <si>
     <t>TEST CASE</t>
   </si>
   <si>
     <t>Test requirement:</t>
+  </si>
+  <si>
+    <t>System Name：</t>
+  </si>
+  <si>
+    <t>SpringMediCareWeb</t>
+  </si>
+  <si>
+    <t>Module Code：</t>
   </si>
   <si>
     <t>Pass</t>
@@ -65,15 +74,6 @@
   </si>
   <si>
     <t>Note</t>
-  </si>
-  <si>
-    <t>System Name：</t>
-  </si>
-  <si>
-    <t>SpringMediCareWeb</t>
-  </si>
-  <si>
-    <t>Module Code：</t>
   </si>
   <si>
     <t>Retest Date</t>
@@ -262,10 +262,11 @@
     <t>Đặt lịch trong khoảng thời gian gần với lịch hẹn đã tồn tại</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân.
-2: Quan sát thấy bác sĩ có lịch hẹn lúc cùng ngày lúc 15:30.
-3: Nhập giờ 15:31.
-4: Nhấn nút Đặt lịch.</t>
+    <t>1: Đăng nhập bằng tài khoản bệnh nhân patient_an.
+2: Đặt lịch hẹn với bác sĩ lúc 15:30 vào ngày bác sĩ có làm.
+3: Đăng xuất và đăng nhập bằng tài khoản bệnh nhân patient_chi
+4: Đặt lịch hẹn cùng ngày nhập giờ 15:31
+5: Nhấn nút Đặt lịch</t>
   </si>
   <si>
     <t>Hệ thống không cho phép tạo lịch hẹn trong khoảng thời gian gần với lịch hẹn đã tồn tại và hiển thị thông báo thời gian khám không khả dụng.</t>
@@ -279,13 +280,37 @@
   <si>
     <t>TCBookingRetest8</t>
   </si>
+  <si>
+    <t xml:space="preserve">5. Kiểm tra quyền truy cập chức năng đặt lịch        </t>
+  </si>
+  <si>
+    <t>TC-BOOKING-009</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút Đặt lịch hẹn điều hướng đúng đến bác sĩ được chọn, với người dùng chưa đăng nhập.</t>
+  </si>
+  <si>
+    <t>1: Mở trang bác sĩ.
+2: Chọn một bác sĩ, ví dụ Tran Binh.
+3: Nhấn Đặt lịch hẹn trên đúng card của bác sĩ đó.
+4: Quan sát trang được điều hướng đến.</t>
+  </si>
+  <si>
+    <t>Hệ thống điều hướng sang trang Đặt lịch hẹn khám của đúng bác sĩ đã chọn. Thông tin bác sĩ trên trang đặt lịch tương ứng với Tran Binh. Không điều hướng sang bác sĩ khác và không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>TCBooking9_1, TCBooking9_2</t>
+  </si>
+  <si>
+    <t>Guest chưa đăng nhập vẫn truy cập được trang đặt lịch. Cần bổ sung kiểm tra xác thực trước khi cho phép truy cập chức năng đặt lịch.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="d\-m"/>
+    <numFmt numFmtId="165" formatCode="d\-m"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -293,11 +318,6 @@
       <color rgb="FF000000"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
     </font>
     <font>
       <sz val="11"/>
@@ -313,6 +333,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
     </font>
     <font>
       <b/>
@@ -408,6 +433,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -420,6 +454,39 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -459,122 +526,86 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -819,9 +850,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -848,9 +879,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -877,13 +908,13 @@
     </row>
     <row r="3" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>15</v>
+      <c r="B3" s="31" t="s">
+        <v>3</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -910,13 +941,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="26"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -945,11 +976,11 @@
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -976,13 +1007,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6">
         <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1013,16 +1044,16 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1078,39 +1109,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="A9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="31" t="s">
+      <c r="B9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="34" t="s">
+      <c r="C9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="D9" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="34" t="s">
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="34" t="s">
+      <c r="H9" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="L9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="34" t="s">
+      <c r="M9" s="36" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1129,19 +1160,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1163,14 +1194,14 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1187,21 +1218,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="26"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1227,11 +1258,11 @@
       <c r="C13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="17" t="s">
         <v>28</v>
       </c>
@@ -1239,7 +1270,7 @@
         <v>46226</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>29</v>
@@ -1263,21 +1294,21 @@
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="26"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1303,11 +1334,11 @@
       <c r="C15" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="17" t="s">
         <v>35</v>
       </c>
@@ -1315,7 +1346,7 @@
         <v>46226</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>36</v>
@@ -1348,11 +1379,11 @@
       <c r="C16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
       <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
@@ -1360,7 +1391,7 @@
         <v>46226</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>42</v>
@@ -1393,11 +1424,11 @@
       <c r="C17" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="17" t="s">
         <v>47</v>
       </c>
@@ -1405,7 +1436,7 @@
         <v>46226</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>48</v>
@@ -1429,21 +1460,21 @@
       <c r="AA17" s="3"/>
     </row>
     <row r="18" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="26"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1469,11 +1500,11 @@
       <c r="C19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
       <c r="G19" s="17" t="s">
         <v>54</v>
       </c>
@@ -1481,7 +1512,7 @@
         <v>46226</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>55</v>
@@ -1514,11 +1545,11 @@
       <c r="C20" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D20" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
       <c r="G20" s="17" t="s">
         <v>60</v>
       </c>
@@ -1526,7 +1557,7 @@
         <v>46226</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>55</v>
@@ -1550,21 +1581,21 @@
       <c r="AA20" s="3"/>
     </row>
     <row r="21" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="26"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -1590,11 +1621,11 @@
       <c r="C22" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
       <c r="G22" s="17" t="s">
         <v>65</v>
       </c>
@@ -1602,7 +1633,7 @@
         <v>46226</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>55</v>
@@ -1625,7 +1656,7 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>66</v>
       </c>
@@ -1635,11 +1666,11 @@
       <c r="C23" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="37" t="s">
+      <c r="D23" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
       <c r="G23" s="17" t="s">
         <v>70</v>
       </c>
@@ -1647,7 +1678,7 @@
         <v>46226</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>71</v>
@@ -1656,26 +1687,28 @@
         <v>46226</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M23" s="21" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+      <c r="A24" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="26"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -1691,20 +1724,36 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
+    <row r="25" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="18">
+        <v>46252</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="22"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -1751,7 +1800,7 @@
     </row>
     <row r="27" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -29996,22 +30045,24 @@
       <c r="AA1000" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="30">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="L9:L10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="F11:M11"/>
     <mergeCell ref="A12:M12"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
@@ -30036,6 +30087,7 @@
     <hyperlink ref="G22" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
     <hyperlink ref="G23" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
     <hyperlink ref="M23" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="G25" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestCases/Booking_TestCase.xlsx
+++ b/TestCases/Booking_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65AC02F-5AC2-4526-A2DE-D206E40DBE6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419576DF-126D-4439-8B98-305FF430BCB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12012" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BOOKING" sheetId="5" r:id="rId1"/>
+    <sheet name="BOOKING" sheetId="6" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -28,7 +28,13 @@
     <t>TEST CASE</t>
   </si>
   <si>
-    <t>Test requirement:</t>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
   <si>
     <t>System Name：</t>
@@ -40,13 +46,7 @@
     <t>Module Code：</t>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Fail</t>
+    <t>Test requirement:</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -88,10 +88,10 @@
     <t xml:space="preserve">4. Kiểm tra xử lý sau khi đăng nhập        </t>
   </si>
   <si>
-    <t>BOOKING100 - Appointment Booking</t>
+    <t>BOOKING - Appointment Booking</t>
   </si>
   <si>
-    <t>BOOKING1 - Create Appointment</t>
+    <t>Appointment Booking</t>
   </si>
   <si>
     <t>1. Kiểm tra hiển thị thông tin đặt lịch</t>
@@ -103,13 +103,12 @@
     <t>Đặt lịch thành công với ngày và giờ hợp lệ</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn một bác sĩ
-3: Mở trang đặt lịch
-4: Chọn ngày bác sĩ có lịch làm việc
-5: Chọn giờ nằm trong ca làm việc và chưa có người đặt
-6: Nhập ghi chú
-7: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Bác sĩ và chọn bác sĩ cần đặt lịch.
+3: Mở trang Đặt lịch và kiểm tra đúng thông tin bác sĩ đã chọn.
+4: Chọn ngày và giờ hợp lệ, còn trống trong lịch làm việc của bác sĩ.
+5: Nhập ghi chú hợp lệ và nhấn Đặt lịch.
+6: Kiểm tra thông báo thành công và lịch hẹn vừa được tạo.</t>
   </si>
   <si>
     <t>Hệ thống tạo lịch hẹn thành công, hiển thị thông báo đặt lịch thành công và giờ vừa đặt xuất hiện trong danh sách giờ đã được đặt</t>
@@ -127,14 +126,15 @@
     <t>TC-BOOKING-002</t>
   </si>
   <si>
-    <t>Bỏ trống ngày khám</t>
+    <t>Kiểm tra không thể đặt lịch khi chưa chọn ngày khám.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn bác sĩ và mở trang đặt lịch
-3: Không chọn ngày khám
-4: Để các trường còn lại ở trạng thái mặc định
-5: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Đặt lịch của bác sĩ cần đặt.
+3: Để trống ngày khám.
+4: Chọn giờ khám và nhập ghi chú hợp lệ.
+5: Nhấn Đặt lịch.
+6: Kiểm tra thông báo validation và xác nhận lịch hẹn không được tạo.</t>
   </si>
   <si>
     <t>Hệ thống yêu cầu người dùng chọn ngày khám và không tạo lịch hẹn</t>
@@ -149,14 +149,15 @@
     <t>TC-BOOKING-003</t>
   </si>
   <si>
-    <t>Bỏ trống giờ khám</t>
+    <t>Kiểm tra không thể đặt lịch khi chưa chọn giờ khám.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn bác sĩ và mở trang đặt lịch
-3: Không chọn giờ khám
-4: Để các trường còn lại nhập đủ
-5: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Đặt lịch của bác sĩ cần đặt.
+3: Chọn một ngày bác sĩ có lịch làm việc.
+4: Để trống giờ khám và nhập ghi chú hợp lệ.
+5: Nhấn Đặt lịch.
+6: Kiểm tra thông báo validation và xác nhận lịch hẹn không được tạo.</t>
   </si>
   <si>
     <t>Hệ thống yêu cầu người dùng nhập giờ khám và không tạo lịch hẹn</t>
@@ -171,15 +172,15 @@
     <t>TC-BOOKING-004</t>
   </si>
   <si>
-    <t>Bỏ trống ghi chú</t>
+    <t>Kiểm tra đặt lịch khi không nhập ghi chú.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn bác sĩ và mở trang đặt lịch
-3: Chọn ngày bác sĩ có lịch làm việc
-4: Chọn giờ hợp lệ và chưa có người đặt
-5: Để trống ghi chú
-6: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Đặt lịch của bác sĩ cần đặt.
+3: Chọn ngày và giờ hợp lệ, còn trống trong lịch làm việc của bác sĩ.
+4: Để trống trường ghi chú.
+5: Nhấn Đặt lịch.
+6: Kiểm tra kết quả đặt lịch.</t>
   </si>
   <si>
     <t>Hệ thống vẫn tạo lịch hẹn thành công vì ghi chú là thông tin không bắt buộc</t>
@@ -197,18 +198,18 @@
     <t>TC-BOOKING-005</t>
   </si>
   <si>
-    <t>Chọn ngày bác sĩ không có lịch làm việc</t>
+    <t>Kiểm tra không thể đặt lịch vào ngày bác sĩ không có lịch làm việc.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn bác sĩ và mở trang đặt lịch
-3: Chọn ngày bác sĩ không có lịch làm việc
-4: Quan sát thông tin lịch làm việc
-5: Nhập giờ khám
-6: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Đặt lịch của bác sĩ cần đặt.
+3: Chọn một ngày bác sĩ không có lịch làm việc.
+4: Kiểm tra trạng thái thời gian đặt lịch của ngày đã chọn.
+5: Thực hiện đặt lịch nếu hệ thống cho phép thao tác.
+6: Kiểm tra lịch hẹn không được tạo.</t>
   </si>
   <si>
-    <t>Hệ thống hiển thị bác sĩ không có lịch làm việc trong ngày này, không tạo lịch hẹn</t>
+    <t>Hệ thống không cho phép Patient đặt lịch vào ngày bác sĩ không làm việc và không tạo lịch hẹn mới.</t>
   </si>
   <si>
     <t>TCBooking5</t>
@@ -220,14 +221,15 @@
     <t>TC-BOOKING-006</t>
   </si>
   <si>
-    <t>Chọn giờ ngoài lịch làm việc của bác sĩ</t>
+    <t>Kiểm tra không thể đặt lịch vào giờ nằm ngoài ca làm việc của bác sĩ.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn bác sĩ và mở trang đặt lịch
-3: Chọn ngày bác sĩ có lịch làm việc
-4: Nhập giờ nằm ngoài các ca làm việc, ví dụ 12:00
-5: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Đặt lịch của bác sĩ cần đặt.
+3: Chọn một ngày bác sĩ có lịch làm việc.
+4: Chọn hoặc nhập giờ nằm ngoài ca làm việc của bác sĩ.
+5: Thực hiện đặt lịch.
+6: Kiểm tra thông báo và xác nhận lịch hẹn không được tạo.</t>
   </si>
   <si>
     <t>Hệ thống không tạo lịch hẹn và hiển thị thông báo bác sĩ không làm việc vào thời gian đã chọn</t>
@@ -239,15 +241,15 @@
     <t>TC-BOOKING-007</t>
   </si>
   <si>
-    <t>Đặt lịch trùng với giờ đã có bệnh nhân đặt</t>
+    <t>Kiểm tra không thể đặt lịch trùng với giờ đã có lịch hẹn.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân
-2: Chọn bác sĩ và mở trang đặt lịch
-3: Chọn ngày có giờ đã được đặt
-4: Quan sát danh sách giờ đã được đặt
-5: Nhập một giờ đang hiển thị trong danh sách
-6: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Mở trang Đặt lịch của bác sĩ cần đặt.
+3: Xác định ngày và giờ đã có lịch hẹn của bác sĩ.
+4: Chọn lại đúng ngày và giờ đã có lịch hẹn.
+5: Nhấn Đặt lịch.
+6: Kiểm tra thông báo và xác nhận không phát sinh lịch hẹn trùng.</t>
   </si>
   <si>
     <t>Hệ thống không tạo lịch hẹn mới và hiển thị thông báo giờ đã có người đặt</t>
@@ -259,17 +261,18 @@
     <t>TC-BOOKING-008</t>
   </si>
   <si>
-    <t>Đặt lịch trong khoảng thời gian gần với lịch hẹn đã tồn tại</t>
+    <t>Kiểm tra không thể đặt lịch cách một lịch hẹn hiện có dưới 30 phút.</t>
   </si>
   <si>
-    <t>1: Đăng nhập bằng tài khoản bệnh nhân patient_an.
-2: Đặt lịch hẹn với bác sĩ lúc 15:30 vào ngày bác sĩ có làm.
-3: Đăng xuất và đăng nhập bằng tài khoản bệnh nhân patient_chi
-4: Đặt lịch hẹn cùng ngày nhập giờ 15:31
-5: Nhấn nút Đặt lịch</t>
+    <t>1: Đăng nhập bằng tài khoản Patient hợp lệ.
+2: Xác định một lịch hẹn đã tồn tại của bác sĩ.
+3: Mở trang Đặt lịch của cùng bác sĩ.
+4: Chọn cùng ngày và một giờ cách lịch hẹn hiện có dưới 30 phút.
+5: Nhấn Đặt lịch.
+6: Kiểm tra thông báo và xác nhận lịch hẹn mới không được tạo.</t>
   </si>
   <si>
-    <t>Hệ thống không cho phép tạo lịch hẹn trong khoảng thời gian gần với lịch hẹn đã tồn tại và hiển thị thông báo thời gian khám không khả dụng.</t>
+    <t>Hệ thống từ chối thời gian cách lịch hẹn hiện có dưới 30 phút và không tạo lịch hẹn mới.</t>
   </si>
   <si>
     <t>TCBooking8</t>
@@ -287,16 +290,18 @@
     <t>TC-BOOKING-009</t>
   </si>
   <si>
-    <t>Kiểm tra nút Đặt lịch hẹn điều hướng đúng đến bác sĩ được chọn, với người dùng chưa đăng nhập.</t>
+    <t>Kiểm tra người dùng chưa đăng nhập không được truy cập chức năng Đặt lịch hẹn.</t>
   </si>
   <si>
-    <t>1: Mở trang bác sĩ.
-2: Chọn một bác sĩ, ví dụ Tran Binh.
-3: Nhấn Đặt lịch hẹn trên đúng card của bác sĩ đó.
-4: Quan sát trang được điều hướng đến.</t>
+    <t>1: Đảm bảo người dùng đang ở trạng thái chưa đăng nhập.
+2: Mở trang Bác sĩ.
+3: Chọn bác sĩ cần đặt lịch.
+4: Nhấn nút Đặt lịch hẹn.
+5: Kiểm tra trang được điều hướng đến.
+6: Xác nhận Guest không thể truy cập form Đặt lịch.</t>
   </si>
   <si>
-    <t>Hệ thống điều hướng sang trang Đặt lịch hẹn khám của đúng bác sĩ đã chọn. Thông tin bác sĩ trên trang đặt lịch tương ứng với Tran Binh. Không điều hướng sang bác sĩ khác và không phát sinh lỗi.</t>
+    <t>Hệ thống không cho phép người dùng chưa đăng nhập truy cập form Đặt lịch và yêu cầu đăng nhập trước khi tiếp tục. Không có lịch hẹn nào được tạo.</t>
   </si>
   <si>
     <t>TCBooking9_1, TCBooking9_2</t>
@@ -321,7 +326,8 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="MS PGothic"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
     </font>
     <font>
       <b/>
@@ -336,8 +342,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -409,6 +414,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -424,30 +453,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -535,78 +540,78 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -827,7 +832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -850,9 +855,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -879,9 +884,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -908,13 +913,13 @@
     </row>
     <row r="3" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>3</v>
+      <c r="B3" s="27" t="s">
+        <v>5</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="26"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -941,13 +946,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="26"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -974,13 +979,13 @@
     </row>
     <row r="5" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1007,13 +1012,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" s="6">
         <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1044,7 +1049,7 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6">
         <v>2</v>
@@ -1109,21 +1114,21 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="33" t="s">
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="31" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="36" t="s">
@@ -1160,19 +1165,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1195,13 +1200,13 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="37"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1221,18 +1226,18 @@
       <c r="A12" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1248,7 +1253,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>24</v>
       </c>
@@ -1261,8 +1266,8 @@
       <c r="D13" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="17" t="s">
         <v>28</v>
       </c>
@@ -1270,7 +1275,7 @@
         <v>46226</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>29</v>
@@ -1297,18 +1302,18 @@
       <c r="A14" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="29"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1324,7 +1329,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>31</v>
       </c>
@@ -1337,8 +1342,8 @@
       <c r="D15" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="17" t="s">
         <v>35</v>
       </c>
@@ -1346,7 +1351,7 @@
         <v>46226</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>36</v>
@@ -1369,7 +1374,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>37</v>
       </c>
@@ -1382,8 +1387,8 @@
       <c r="D16" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="17" t="s">
         <v>41</v>
       </c>
@@ -1391,7 +1396,7 @@
         <v>46226</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>42</v>
@@ -1414,7 +1419,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>43</v>
       </c>
@@ -1427,8 +1432,8 @@
       <c r="D17" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
       <c r="G17" s="17" t="s">
         <v>47</v>
       </c>
@@ -1436,7 +1441,7 @@
         <v>46226</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>48</v>
@@ -1463,18 +1468,18 @@
       <c r="A18" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="29"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1503,8 +1508,8 @@
       <c r="D19" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="17" t="s">
         <v>54</v>
       </c>
@@ -1512,7 +1517,7 @@
         <v>46226</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>55</v>
@@ -1535,7 +1540,7 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>56</v>
       </c>
@@ -1548,8 +1553,8 @@
       <c r="D20" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
       <c r="G20" s="17" t="s">
         <v>60</v>
       </c>
@@ -1557,7 +1562,7 @@
         <v>46226</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>55</v>
@@ -1584,18 +1589,18 @@
       <c r="A21" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="29"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -1611,7 +1616,7 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>61</v>
       </c>
@@ -1624,8 +1629,8 @@
       <c r="D22" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="17" t="s">
         <v>65</v>
       </c>
@@ -1633,7 +1638,7 @@
         <v>46226</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>55</v>
@@ -1656,7 +1661,7 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="125.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>66</v>
       </c>
@@ -1669,8 +1674,8 @@
       <c r="D23" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="17" t="s">
         <v>70</v>
       </c>
@@ -1678,7 +1683,7 @@
         <v>46226</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>71</v>
@@ -1687,7 +1692,7 @@
         <v>46226</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M23" s="21" t="s">
         <v>72</v>
@@ -1697,18 +1702,18 @@
       <c r="A24" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="26"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="29"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -1724,7 +1729,7 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>74</v>
       </c>
@@ -1737,8 +1742,8 @@
       <c r="D25" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
       <c r="G25" s="17" t="s">
         <v>78</v>
       </c>
@@ -1746,7 +1751,7 @@
         <v>46252</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>79</v>
@@ -30078,16 +30083,16 @@
     <mergeCell ref="D9:F10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
-    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
-    <hyperlink ref="G19" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
-    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
-    <hyperlink ref="G22" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
-    <hyperlink ref="G23" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
-    <hyperlink ref="M23" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
-    <hyperlink ref="G25" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="G19" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="G22" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="G23" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="M23" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
+    <hyperlink ref="G25" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
